--- a/other/データベース構造.xlsx
+++ b/other/データベース構造.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\take8\OneDrive\ドキュメント\java\material-flow-rate-adjustment\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963B61B4-CCD7-43D0-B4BC-3BA1437937F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711D9473-6C50-4929-8D7B-770064991136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{099D4C76-A145-49FD-90AD-E407201FC483}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="33">
   <si>
     <t>id
 (INT,
@@ -104,13 +104,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>achievement
-(INT,
-UNSIGNED,
-NOT NULL)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>remaining
 (INT,
 UNSIGNED,
@@ -141,12 +134,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>user
-(VARCHAR(10)
-NOT NULL,)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>作業者A</t>
     <rPh sb="0" eb="3">
       <t>サギョウシャ</t>
@@ -184,6 +171,74 @@
   <si>
     <t>pass
 (BOOLEAN,
+NOT NULL)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>adjustment</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓別テーブルから算出</t>
+    <rPh sb="1" eb="2">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サンシュツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓テーブルにはない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>管理者A</t>
+    <rPh sb="0" eb="3">
+      <t>カンリシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>管理者B</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>管理者A</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理由を書く</t>
+    <rPh sb="0" eb="2">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>adjustment_id
+(INT,
+UNSIGNED,
+NOT NULL)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>user
+(VARCHAR(20)
+NOT NULL,)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>reason
+(VARCHAR(50)
+NOT NULL,)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>quantity
+(INT,
 NOT NULL)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -192,7 +247,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,6 +258,30 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -246,7 +325,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -268,6 +347,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -283,6 +371,170 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>693420</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="直線矢印コネクタ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DE7BCED-881B-4E4B-A12E-2F4F9D08924B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1363980" y="2537460"/>
+          <a:ext cx="1150620" cy="434340"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>769620</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="直線矢印コネクタ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7A2B899-ED44-4629-93E1-A56C6E2B98E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1440180" y="5036820"/>
+          <a:ext cx="1150620" cy="434340"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>746760</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="直線矢印コネクタ 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3896E6AC-6605-45F5-BC6D-707DC1D7379C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1417320" y="5013960"/>
+          <a:ext cx="1196340" cy="2994660"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -582,17 +834,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E535CC99-BAB4-4269-ACB1-CBFC0A25D5CA}">
-  <dimension ref="B2:K21"/>
+  <dimension ref="B2:K28"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="16.8984375" customWidth="1"/>
-    <col min="5" max="5" width="11.69921875" customWidth="1"/>
+    <col min="5" max="5" width="13.69921875" customWidth="1"/>
     <col min="6" max="6" width="13.796875" customWidth="1"/>
-    <col min="7" max="7" width="11.69921875" customWidth="1"/>
+    <col min="7" max="7" width="15.3984375" customWidth="1"/>
     <col min="8" max="8" width="11.296875" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
+    <col min="9" max="10" width="11" customWidth="1"/>
     <col min="11" max="11" width="37.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -635,23 +887,37 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="G8" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>6</v>
       </c>
+      <c r="G9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="10" spans="2:11" ht="90" x14ac:dyDescent="0.45">
       <c r="B10" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>7</v>
@@ -662,17 +928,20 @@
       <c r="F10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="K10" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.45">
@@ -691,14 +960,17 @@
       <c r="F11" s="3">
         <v>1000</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="8">
         <v>950</v>
       </c>
       <c r="H11" s="3">
         <v>900</v>
       </c>
-      <c r="I11" s="3">
-        <f>(0+G11)-H11</f>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <f>(0+G11+I11)-H11</f>
         <v>50</v>
       </c>
     </row>
@@ -718,14 +990,17 @@
       <c r="F12" s="3">
         <v>1500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="8">
         <v>1550</v>
       </c>
       <c r="H12" s="3">
         <v>1500</v>
       </c>
-      <c r="I12" s="3">
-        <f>(I11+G12)-H12</f>
+      <c r="I12" s="8">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <f>(J11+G12+I12)-H12</f>
         <v>100</v>
       </c>
     </row>
@@ -745,41 +1020,47 @@
       <c r="F13" s="3">
         <v>1000</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="8">
         <v>1000</v>
       </c>
       <c r="H13" s="3">
         <v>1050</v>
       </c>
-      <c r="I13" s="3">
-        <f>(I12+G13)-H13</f>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <f>(J12+G13+I13)-H13</f>
         <v>50</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B14" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.45">
@@ -792,25 +1073,25 @@
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.45">
@@ -830,7 +1111,7 @@
         <v>50</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H18" s="3">
         <v>1</v>
@@ -853,7 +1134,7 @@
         <v>50</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H19" s="3">
         <v>0</v>
@@ -876,7 +1157,7 @@
         <v>50</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H20" s="3">
         <v>1</v>
@@ -884,27 +1165,134 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" ht="90" x14ac:dyDescent="0.45">
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H21" s="3"/>
+      <c r="E24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1</v>
+      </c>
+      <c r="D25" s="4">
+        <v>44136.424305555556</v>
+      </c>
+      <c r="E25" s="2">
+        <v>10</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B26" s="3">
+        <v>2</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1</v>
+      </c>
+      <c r="D26" s="4">
+        <v>44136.690972222219</v>
+      </c>
+      <c r="E26" s="2">
+        <v>-5</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B27" s="3">
+        <v>3</v>
+      </c>
+      <c r="C27" s="3">
+        <v>1</v>
+      </c>
+      <c r="D27" s="4">
+        <v>44137.420138888891</v>
+      </c>
+      <c r="E27" s="2">
+        <v>-5</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/other/データベース構造.xlsx
+++ b/other/データベース構造.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\take8\OneDrive\ドキュメント\java\material-flow-rate-adjustment\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711D9473-6C50-4929-8D7B-770064991136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1215D744-DBDA-430F-9FC8-50F24262BA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{099D4C76-A145-49FD-90AD-E407201FC483}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="43">
   <si>
     <t>id
 (INT,
@@ -240,6 +240,53 @@
     <t>quantity
 (INT,
 NOT NULL)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>account</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>user
+(VARCHAR(20),
+UNIQUE,
+NOT NULL,)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>password
+(VARCHAR(255)
+NOT NULL,)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>role
+(VARCHAR(10)
+NOT NULL,)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ADMIN</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>USER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MANAGER</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●●●●●●</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●●●●</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●●●●●●●</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -834,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E535CC99-BAB4-4269-ACB1-CBFC0A25D5CA}">
-  <dimension ref="B2:K28"/>
+  <dimension ref="B2:K35"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="17.5" customWidth="1"/>
@@ -1290,6 +1337,81 @@
       </c>
       <c r="G28" s="3"/>
     </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" ht="90" x14ac:dyDescent="0.45">
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B32" s="3">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B33" s="3">
+        <v>2</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B34" s="3">
+        <v>3</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/other/データベース構造.xlsx
+++ b/other/データベース構造.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\take8\OneDrive\ドキュメント\java\material-flow-rate-adjustment\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1215D744-DBDA-430F-9FC8-50F24262BA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC3C5BD-249E-4131-A4B0-3218F894EBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{099D4C76-A145-49FD-90AD-E407201FC483}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="58">
   <si>
     <t>id
 (INT,
@@ -289,12 +289,99 @@
     <t>●●●●●●●</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>メインのテーブル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>履歴用のテーブル</t>
+    <rPh sb="0" eb="2">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CREATE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CHANGE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DELETE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>account_history</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>date
+(DATETIME,
+DEFAULT, CURRENT_TIMESTAMP,
+INSERTABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>old_user
+(VARCHAR(20),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>new_user
+(VARCHAR(20),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>old_role
+(VARCHAR(10),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>new_role
+(VARCHAR(10),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>action
+(VARCHAR(10),
+NOT NULL,
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>action_user
+(VARCHAR(20),
+NOT NULL,
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>action_id
+(INT,
+UNSIGNED,
+NOT NULL,
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,6 +421,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -343,7 +439,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -366,13 +462,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -403,6 +514,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -426,13 +540,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>693420</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>510540</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -479,13 +593,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>769620</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>586740</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -532,13 +646,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>746760</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -881,149 +995,127 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E535CC99-BAB4-4269-ACB1-CBFC0A25D5CA}">
-  <dimension ref="B2:K35"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="1" max="1" width="17.09765625" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
-    <col min="4" max="4" width="16.8984375" customWidth="1"/>
-    <col min="5" max="5" width="13.69921875" customWidth="1"/>
-    <col min="6" max="6" width="13.796875" customWidth="1"/>
-    <col min="7" max="7" width="15.3984375" customWidth="1"/>
-    <col min="8" max="8" width="11.296875" customWidth="1"/>
-    <col min="9" max="10" width="11" customWidth="1"/>
+    <col min="4" max="4" width="21.8984375" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="19.69921875" customWidth="1"/>
+    <col min="7" max="7" width="20.296875" customWidth="1"/>
+    <col min="8" max="8" width="20.09765625" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="22.09765625" customWidth="1"/>
     <col min="11" max="11" width="37.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B2" t="s">
+    <row r="1" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="2" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="90" x14ac:dyDescent="0.45">
-      <c r="B3" s="1" t="s">
+    <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.45">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B5" s="3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B6" s="3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B7" s="3">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="G8" s="9" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="G9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G10" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I10" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="90" x14ac:dyDescent="0.45">
-      <c r="B10" s="1" t="s">
+    <row r="11" spans="1:11" ht="90" x14ac:dyDescent="0.45">
+      <c r="B11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="J11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K11" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B11" s="3">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3">
-        <v>1</v>
-      </c>
-      <c r="D11" s="3">
-        <v>2020</v>
-      </c>
-      <c r="E11" s="3">
-        <v>11</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G11" s="8">
-        <v>950</v>
-      </c>
-      <c r="H11" s="3">
-        <v>900</v>
-      </c>
-      <c r="I11" s="8">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <f>(0+G11+I11)-H11</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1032,268 +1124,278 @@
         <v>2020</v>
       </c>
       <c r="E12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="3">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="G12" s="8">
-        <v>1550</v>
+        <v>950</v>
       </c>
       <c r="H12" s="3">
-        <v>1500</v>
+        <v>900</v>
       </c>
       <c r="I12" s="8">
         <v>0</v>
       </c>
       <c r="J12" s="3">
-        <f>(J11+G12+I12)-H12</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
+        <f>(0+G12+I12)-H12</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B13" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="3">
         <v>1</v>
       </c>
       <c r="D13" s="3">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E13" s="3">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F13" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="G13" s="8">
-        <v>1000</v>
+        <v>1550</v>
       </c>
       <c r="H13" s="3">
-        <v>1050</v>
+        <v>1500</v>
       </c>
       <c r="I13" s="8">
         <v>0</v>
       </c>
       <c r="J13" s="3">
         <f>(J12+G13+I13)-H13</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B14" s="3">
+        <v>3</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2021</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1000</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1050</v>
+      </c>
+      <c r="I14" s="8">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <f>(J13+G14+I14)-H14</f>
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="B15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="90" x14ac:dyDescent="0.45">
-      <c r="B17" s="1" t="s">
+    <row r="18" spans="2:11" ht="90" x14ac:dyDescent="0.45">
+      <c r="B18" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K18" s="5" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B18" s="3">
-        <v>1</v>
-      </c>
-      <c r="C18" s="3">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4">
-        <v>44136.424305555556</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1111</v>
-      </c>
-      <c r="F18" s="2">
-        <v>50</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B19" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" s="3">
         <v>1</v>
       </c>
       <c r="D19" s="4">
-        <v>44136.690972222219</v>
+        <v>44136.424305555556</v>
       </c>
       <c r="E19" s="2">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="F19" s="2">
         <v>50</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H19" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B20" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
       </c>
       <c r="D20" s="4">
-        <v>44137.420138888891</v>
+        <v>44136.690972222219</v>
       </c>
       <c r="E20" s="2">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="F20" s="2">
         <v>50</v>
       </c>
       <c r="G20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B21" s="3">
+        <v>3</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" s="4">
+        <v>44137.420138888891</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1115</v>
+      </c>
+      <c r="F21" s="2">
+        <v>50</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H20" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" s="3"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="90" x14ac:dyDescent="0.45">
-      <c r="B24" s="1" t="s">
+    <row r="25" spans="2:11" ht="126" x14ac:dyDescent="0.45">
+      <c r="B25" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E24" s="1" t="s">
+      <c r="D25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G25" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="K24" s="5" t="s">
+      <c r="K25" s="5" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B25" s="3">
-        <v>1</v>
-      </c>
-      <c r="C25" s="3">
-        <v>1</v>
-      </c>
-      <c r="D25" s="4">
-        <v>44136.424305555556</v>
-      </c>
-      <c r="E25" s="2">
-        <v>10</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B26" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
       </c>
       <c r="D26" s="4">
-        <v>44136.690972222219</v>
+        <v>44136.424305555556</v>
       </c>
       <c r="E26" s="2">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>28</v>
@@ -1301,114 +1403,274 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B27" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="3">
         <v>1</v>
       </c>
       <c r="D27" s="4">
-        <v>44137.420138888891</v>
+        <v>44136.690972222219</v>
       </c>
       <c r="E27" s="2">
         <v>-5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="3"/>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
+      <c r="B28" s="3">
+        <v>3</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1</v>
+      </c>
+      <c r="D28" s="4">
+        <v>44137.420138888891</v>
+      </c>
+      <c r="E28" s="2">
+        <v>-5</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29" s="3"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="2:11" ht="90" x14ac:dyDescent="0.45">
-      <c r="B31" s="1" t="s">
+    <row r="32" spans="2:11" ht="90" x14ac:dyDescent="0.45">
+      <c r="B32" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B32" s="3">
-        <v>1</v>
-      </c>
-      <c r="C32" s="2" t="s">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B33" s="3">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B33" s="3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B34" s="3">
         <v>2</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B34" s="3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B35" s="3">
         <v>3</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="3" t="s">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="38" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A38" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="90" x14ac:dyDescent="0.45">
+      <c r="B40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B41" s="3">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H41" s="2">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" s="4">
+        <v>44136.424305555556</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B42" s="3">
+        <v>2</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H42" s="2">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" s="4">
+        <v>44136.690972222219</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B43" s="3">
+        <v>3</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H43" s="2">
+        <v>1</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J43" s="4">
+        <v>44137.420138888891</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="B44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J44" s="3" t="s">
         <v>13</v>
       </c>
     </row>

--- a/other/データベース構造.xlsx
+++ b/other/データベース構造.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\take8\OneDrive\ドキュメント\java\material-flow-rate-adjustment\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC3C5BD-249E-4131-A4B0-3218F894EBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87830E74-8EF1-484F-840D-99E34DAEEA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{099D4C76-A145-49FD-90AD-E407201FC483}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="59">
   <si>
     <t>id
 (INT,
@@ -370,6 +370,14 @@
   </si>
   <si>
     <t>action_id
+(INT,
+UNSIGNED,
+NOT NULL,
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>target_id
 (INT,
 UNSIGNED,
 NOT NULL,
@@ -1478,7 +1486,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B33" s="3">
         <v>1</v>
       </c>
@@ -1492,7 +1500,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B34" s="3">
         <v>2</v>
       </c>
@@ -1506,7 +1514,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B35" s="3">
         <v>3</v>
       </c>
@@ -1520,7 +1528,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
         <v>13</v>
       </c>
@@ -1534,118 +1542,130 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="38" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="38" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" s="10" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="90" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" ht="90" x14ac:dyDescent="0.45">
       <c r="B40" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="J40" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="K40" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B41" s="3">
         <v>1</v>
       </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2" t="s">
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="2"/>
+      <c r="G41" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="H41" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H41" s="2">
-        <v>1</v>
-      </c>
-      <c r="I41" s="2" t="s">
+      <c r="I41" s="2">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J41" s="4">
+      <c r="K41" s="4">
         <v>44136.424305555556</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B42" s="3">
         <v>2</v>
       </c>
-      <c r="C42" s="2"/>
+      <c r="C42" s="2">
+        <v>1</v>
+      </c>
       <c r="D42" s="2"/>
-      <c r="E42" s="2" t="s">
+      <c r="E42" s="2"/>
+      <c r="F42" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="G42" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="H42" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H42" s="2">
-        <v>1</v>
-      </c>
-      <c r="I42" s="2" t="s">
+      <c r="I42" s="2">
+        <v>1</v>
+      </c>
+      <c r="J42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J42" s="4">
+      <c r="K42" s="4">
         <v>44136.690972222219</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B43" s="3">
         <v>3</v>
       </c>
-      <c r="C43" s="2"/>
+      <c r="C43" s="2">
+        <v>1</v>
+      </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="2"/>
+      <c r="H43" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="H43" s="2">
-        <v>1</v>
-      </c>
-      <c r="I43" s="2" t="s">
+      <c r="I43" s="2">
+        <v>2</v>
+      </c>
+      <c r="J43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J43" s="4">
+      <c r="K43" s="4">
         <v>44137.420138888891</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B44" s="3" t="s">
         <v>13</v>
       </c>
@@ -1671,6 +1691,9 @@
         <v>13</v>
       </c>
       <c r="J44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="K44" s="3" t="s">
         <v>13</v>
       </c>
     </row>

--- a/other/データベース構造.xlsx
+++ b/other/データベース構造.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\take8\OneDrive\ドキュメント\java\material-flow-rate-adjustment\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87830E74-8EF1-484F-840D-99E34DAEEA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B975967E-6D46-4CA0-8D8D-C26AF965A7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{099D4C76-A145-49FD-90AD-E407201FC483}"/>
   </bookViews>
@@ -34,19 +34,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="71">
   <si>
     <t>id
 (INT,
 AUTO_INCREMENT,
 NOT NULL,
 PRIMARY KEY)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>name
-(VARCHAR(30)
-NOT NULL,)</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -225,12 +219,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>user
-(VARCHAR(20)
-NOT NULL,)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>reason
 (VARCHAR(50)
 NOT NULL,)</t>
@@ -244,13 +232,6 @@
   </si>
   <si>
     <t>account</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>user
-(VARCHAR(20),
-UNIQUE,
-NOT NULL,)</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -304,10 +285,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>b</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>CREATE</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -331,18 +308,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>old_user
-(VARCHAR(20),
-UPDATABLE=FALSE)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>new_user
-(VARCHAR(20),
-UPDATABLE=FALSE)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>old_role
 (VARCHAR(10),
 UPDATABLE=FALSE)</t>
@@ -357,13 +322,6 @@
   <si>
     <t>action
 (VARCHAR(10),
-NOT NULL,
-UPDATABLE=FALSE)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>action_user
-(VARCHAR(20),
 NOT NULL,
 UPDATABLE=FALSE)</t>
     <phoneticPr fontId="1"/>
@@ -380,6 +338,119 @@
     <t>target_id
 (INT,
 UNSIGNED,
+NOT NULL,
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>login_user
+(VARCHAR(20),
+UNIQUE,
+NOT NULL,)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>admin_a</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>admin_b</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>old_login_user
+(VARCHAR(20),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>new_login_user
+(VARCHAR(20),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>displayed_user
+(VARCHAR(10),
+UNIQUE,
+NOT NULL,)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>old_displayed_user
+(VARCHAR(10),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>new_displayed_user
+(VARCHAR(10),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>user
+(VARCHAR(10)
+NOT NULL,)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>destination
+(VARCHAR(10)
+NOT NULL)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>name
+(VARCHAR(10)
+NOT NULL)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業A</t>
+    <rPh sb="0" eb="2">
+      <t>キギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>material_history</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>new_material_name
+(VARCHAR(10),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>old_material_name
+(VARCHAR(10),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>old_material_destination
+(VARCHAR(10),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>new_material_destination
+(VARCHAR(10),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業B</t>
+    <rPh sb="0" eb="2">
+      <t>キギョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>action_user
+(VARCHAR(10),
 NOT NULL,
 UPDATABLE=FALSE)</t>
     <phoneticPr fontId="1"/>
@@ -1003,7 +1074,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E535CC99-BAB4-4269-ACB1-CBFC0A25D5CA}">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="17.09765625" customWidth="1"/>
@@ -1011,23 +1082,25 @@
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="21.8984375" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="19.69921875" customWidth="1"/>
-    <col min="7" max="7" width="20.296875" customWidth="1"/>
+    <col min="6" max="6" width="21.3984375" customWidth="1"/>
+    <col min="7" max="7" width="22.5" customWidth="1"/>
     <col min="8" max="8" width="20.09765625" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="22.09765625" customWidth="1"/>
-    <col min="11" max="11" width="37.5" customWidth="1"/>
+    <col min="11" max="11" width="37.296875" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="22.09765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.45">
@@ -1035,7 +1108,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>62</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
@@ -1043,7 +1119,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
@@ -1051,7 +1130,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
@@ -1059,34 +1141,40 @@
         <v>3</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="G9" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="90" x14ac:dyDescent="0.45">
@@ -1094,31 +1182,31 @@
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
@@ -1213,36 +1301,36 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="90" x14ac:dyDescent="0.45">
@@ -1250,25 +1338,25 @@
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.45">
@@ -1288,7 +1376,7 @@
         <v>50</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" s="3">
         <v>1</v>
@@ -1311,7 +1399,7 @@
         <v>50</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1334,7 +1422,7 @@
         <v>50</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H21" s="3">
         <v>1</v>
@@ -1342,51 +1430,51 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H22" s="3"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" ht="126" x14ac:dyDescent="0.45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="90" x14ac:dyDescent="0.45">
       <c r="B25" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="K25" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.45">
@@ -1403,10 +1491,10 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.45">
@@ -1423,10 +1511,10 @@
         <v>-5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.45">
@@ -1443,33 +1531,33 @@
         <v>-5</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" s="3"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="90" x14ac:dyDescent="0.45">
@@ -1477,115 +1565,136 @@
         <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B33" s="3">
         <v>1</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="F33" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B34" s="3">
         <v>2</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="F34" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B35" s="3">
         <v>3</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="F35" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="38" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+        <v>12</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="38" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A38" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="90" x14ac:dyDescent="0.45">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="90" x14ac:dyDescent="0.45">
       <c r="B40" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="G40" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="L40" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B41" s="3">
         <v>1</v>
       </c>
@@ -1594,26 +1703,30 @@
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I41" s="2">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K41" s="4">
+        <v>42</v>
+      </c>
+      <c r="K41" s="2">
+        <v>1</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M41" s="4">
         <v>44136.424305555556</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B42" s="3">
         <v>2</v>
       </c>
@@ -1622,79 +1735,248 @@
       </c>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
       <c r="H42" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I42" s="2">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K42" s="4">
+        <v>43</v>
+      </c>
+      <c r="K42" s="2">
+        <v>1</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M42" s="4">
         <v>44136.690972222219</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B43" s="3">
         <v>3</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
       </c>
-      <c r="D43" s="2"/>
+      <c r="D43" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+      <c r="F43" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I43" s="2">
+        <v>36</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K43" s="2">
         <v>2</v>
       </c>
-      <c r="J43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="K43" s="4">
+      <c r="L43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M43" s="4">
         <v>44137.420138888891</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B44" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="90" x14ac:dyDescent="0.45">
+      <c r="B47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="B48" s="3">
+        <v>1</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I48" s="2">
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K48" s="4">
+        <v>44136.424305555556</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B49" s="3">
+        <v>2</v>
+      </c>
+      <c r="C49" s="2">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I49" s="2">
+        <v>1</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K49" s="4">
+        <v>44136.690972222219</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B50" s="3">
+        <v>3</v>
+      </c>
+      <c r="C50" s="2">
+        <v>1</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I50" s="2">
+        <v>2</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" s="4">
+        <v>44137.420138888891</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/other/データベース構造.xlsx
+++ b/other/データベース構造.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\take8\OneDrive\ドキュメント\java\material-flow-rate-adjustment\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B975967E-6D46-4CA0-8D8D-C26AF965A7A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DA5114-58BB-4F2E-9C29-B5E7972646BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{099D4C76-A145-49FD-90AD-E407201FC483}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="71">
   <si>
     <t>id
 (INT,
@@ -98,20 +98,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>remaining
-(INT,
-UNSIGNED,
-NOT NULL)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>shipping
-(INT,
-UNSIGNED,
-NOT NULL)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>…</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -170,20 +156,6 @@
   </si>
   <si>
     <t>adjustment</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>↓別テーブルから算出</t>
-    <rPh sb="1" eb="2">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>サンシュツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>↓テーブルにはない</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -455,12 +427,35 @@
 UPDATABLE=FALSE)</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>shipping
+(INT,
+UNSIGNED)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>remaining
+(INT,
+UNSIGNED)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>achievement
+(INT,
+UNSIGNED)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>adjustment
+(INT)</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -477,22 +472,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.249977111117893"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="6"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
@@ -504,6 +483,13 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -584,17 +570,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1094,8 +1080,8 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="10" t="s">
-        <v>40</v>
+      <c r="A2" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
@@ -1108,10 +1094,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
@@ -1122,7 +1108,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
@@ -1133,7 +1119,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
@@ -1144,45 +1130,37 @@
         <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="G9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>23</v>
-      </c>
+      <c r="G9" s="7"/>
+      <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>22</v>
-      </c>
+      <c r="G10" s="7"/>
+      <c r="I10" s="7"/>
     </row>
     <row r="11" spans="1:11" ht="90" x14ac:dyDescent="0.45">
       <c r="B11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>6</v>
@@ -1193,20 +1171,20 @@
       <c r="F11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>9</v>
+      <c r="G11" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>21</v>
+        <v>67</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>10</v>
+        <v>68</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
@@ -1225,13 +1203,13 @@
       <c r="F12" s="3">
         <v>1000</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="10">
         <v>950</v>
       </c>
       <c r="H12" s="3">
         <v>900</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="10">
         <v>0</v>
       </c>
       <c r="J12" s="3">
@@ -1255,13 +1233,13 @@
       <c r="F13" s="3">
         <v>1500</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="10">
         <v>1550</v>
       </c>
       <c r="H13" s="3">
         <v>1500</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="10">
         <v>0</v>
       </c>
       <c r="J13" s="3">
@@ -1285,13 +1263,13 @@
       <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="10">
         <v>1000</v>
       </c>
       <c r="H14" s="3">
         <v>1050</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="10">
         <v>0</v>
       </c>
       <c r="J14" s="3">
@@ -1301,31 +1279,31 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.45">
@@ -1338,25 +1316,25 @@
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.45">
@@ -1376,7 +1354,7 @@
         <v>50</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H19" s="3">
         <v>1</v>
@@ -1399,7 +1377,7 @@
         <v>50</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1422,7 +1400,7 @@
         <v>50</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H21" s="3">
         <v>1</v>
@@ -1430,28 +1408,28 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H22" s="3"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="90" x14ac:dyDescent="0.45">
@@ -1459,22 +1437,22 @@
         <v>0</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.45">
@@ -1491,10 +1469,10 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.45">
@@ -1511,10 +1489,10 @@
         <v>-5</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.45">
@@ -1531,33 +1509,33 @@
         <v>-5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G29" s="3"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="90" x14ac:dyDescent="0.45">
@@ -1565,16 +1543,16 @@
         <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.45">
@@ -1582,16 +1560,16 @@
         <v>1</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.45">
@@ -1599,16 +1577,16 @@
         <v>2</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.45">
@@ -1616,44 +1594,44 @@
         <v>3</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B36" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="38" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="10" t="s">
-        <v>41</v>
+      <c r="A38" s="8" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="90" x14ac:dyDescent="0.45">
@@ -1661,37 +1639,37 @@
         <v>0</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="H40" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.45">
@@ -1703,24 +1681,24 @@
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K41" s="2">
         <v>1</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M41" s="4">
         <v>44136.424305555556</v>
@@ -1738,19 +1716,19 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="K42" s="2">
         <v>1</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M42" s="4">
         <v>44136.690972222219</v>
@@ -1764,25 +1742,25 @@
         <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="K43" s="2">
         <v>2</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="M43" s="4">
         <v>44137.420138888891</v>
@@ -1790,45 +1768,45 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="90" x14ac:dyDescent="0.45">
@@ -1836,31 +1814,31 @@
         <v>0</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J47" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="K47" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.45">
@@ -1876,16 +1854,16 @@
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I48" s="2">
         <v>1</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K48" s="4">
         <v>44136.424305555556</v>
@@ -1901,19 +1879,19 @@
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I49" s="2">
         <v>1</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K49" s="4">
         <v>44136.690972222219</v>
@@ -1931,17 +1909,17 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="I50" s="2">
         <v>2</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K50" s="4">
         <v>44137.420138888891</v>
@@ -1949,34 +1927,34 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B51" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/other/データベース構造.xlsx
+++ b/other/データベース構造.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\take8\OneDrive\ドキュメント\java\material-flow-rate-adjustment\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89DA5114-58BB-4F2E-9C29-B5E7972646BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F66453-3B34-483E-B147-60B8264FC579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{099D4C76-A145-49FD-90AD-E407201FC483}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="81">
   <si>
     <t>id
 (INT,
@@ -69,10 +69,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>month_adjustment</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>year
 (INT,
 UNSIGNED,
@@ -138,13 +134,6 @@
     <t>CONSTRAINT material_key
         FOREIGN KEY (material_id) 
         REFERENCES material(id)
-        ON DELETE CASCADE</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>CONSTRAINT month_adjustment_key
-        FOREIGN KEY (month_adjustment_id) 
-        REFERENCES month_adjustment(id)
         ON DELETE CASCADE</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -450,12 +439,89 @@
 (INT)</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>month_plan</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CONSTRAINT month_plan_key
+        FOREIGN KEY (month_adjustment_id) 
+        REFERENCES month_adjustment(id)
+        ON DELETE CASCADE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>base
+(INT,
+UNSIGNED)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↓実績入力時のデフォルト数量</t>
+    <rPh sb="1" eb="3">
+      <t>ジッセキ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>ニュウリョクジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>スウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>unit
+(VARCHAR(10)
+NOT NULL)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>kg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>個</t>
+    <rPh sb="0" eb="1">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>old_base
+(INT,
+UNSIGNED,
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>new_base
+(INT,
+UNSIGNED,
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>old_unit
+(VARCHAR(10),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>new_unit
+(VARCHAR(10),
+UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -492,6 +558,14 @@
       <sz val="11"/>
       <name val="游ゴシック"/>
       <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -548,7 +622,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -581,6 +655,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1060,7 +1137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E535CC99-BAB4-4269-ACB1-CBFC0A25D5CA}">
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="17.09765625" customWidth="1"/>
@@ -1076,28 +1153,39 @@
     <col min="11" max="11" width="37.296875" customWidth="1"/>
     <col min="12" max="12" width="20" customWidth="1"/>
     <col min="13" max="13" width="22.09765625" customWidth="1"/>
+    <col min="14" max="14" width="19.3984375" customWidth="1"/>
+    <col min="15" max="15" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A2" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>4</v>
       </c>
+      <c r="E3" s="11" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.45">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
@@ -1108,7 +1196,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
@@ -1119,7 +1213,11 @@
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
@@ -1130,18 +1228,28 @@
         <v>3</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
@@ -1150,7 +1258,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="G10" s="7"/>
       <c r="I10" s="7"/>
@@ -1160,31 +1268,31 @@
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.45">
@@ -1279,36 +1387,36 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="B15" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="90" x14ac:dyDescent="0.45">
@@ -1316,25 +1424,25 @@
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.45">
@@ -1354,7 +1462,7 @@
         <v>50</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H19" s="3">
         <v>1</v>
@@ -1377,7 +1485,7 @@
         <v>50</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1400,7 +1508,7 @@
         <v>50</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H21" s="3">
         <v>1</v>
@@ -1408,28 +1516,28 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B22" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H22" s="3"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="90" x14ac:dyDescent="0.45">
@@ -1437,22 +1545,22 @@
         <v>0</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="F25" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.45">
@@ -1469,10 +1577,10 @@
         <v>10</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.45">
@@ -1489,10 +1597,10 @@
         <v>-5</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.45">
@@ -1509,33 +1617,33 @@
         <v>-5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B29" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G29" s="3"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="2:11" ht="90" x14ac:dyDescent="0.45">
@@ -1543,136 +1651,136 @@
         <v>0</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="B33" s="3">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B33" s="3">
-        <v>1</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B34" s="3">
         <v>2</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B35" s="3">
         <v>3</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="B36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="38" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A38" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="38" spans="1:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="90" x14ac:dyDescent="0.45">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="90" x14ac:dyDescent="0.45">
       <c r="B40" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="G40" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J40" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="K40" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="L40" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B41" s="3">
         <v>1</v>
       </c>
@@ -1681,30 +1789,30 @@
       </c>
       <c r="D41" s="2"/>
       <c r="E41" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K41" s="2">
         <v>1</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M41" s="4">
         <v>44136.424305555556</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B42" s="3">
         <v>2</v>
       </c>
@@ -1716,25 +1824,25 @@
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K42" s="2">
         <v>1</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M42" s="4">
         <v>44136.690972222219</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B43" s="3">
         <v>3</v>
       </c>
@@ -1742,106 +1850,118 @@
         <v>1</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K43" s="2">
         <v>2</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M43" s="4">
         <v>44137.420138888891</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="90" x14ac:dyDescent="0.45">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="90" x14ac:dyDescent="0.45">
       <c r="B47" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N47" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O47" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B48" s="3">
         <v>1</v>
       </c>
@@ -1854,22 +1974,28 @@
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I48" s="2">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K48" s="4">
+        <v>57</v>
+      </c>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M48" s="2">
+        <v>1</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O48" s="4">
         <v>44136.424305555556</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B49" s="3">
         <v>2</v>
       </c>
@@ -1879,25 +2005,33 @@
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I49" s="2">
-        <v>1</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
       <c r="J49" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K49" s="4">
+        <v>75</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M49" s="2">
+        <v>1</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O49" s="4">
         <v>44136.690972222219</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B50" s="3">
         <v>3</v>
       </c>
@@ -1909,52 +2043,70 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G50" s="2"/>
-      <c r="H50" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I50" s="2">
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M50" s="2">
         <v>2</v>
       </c>
-      <c r="J50" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K50" s="4">
+      <c r="N50" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O50" s="4">
         <v>44137.420138888891</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B51" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/other/データベース構造.xlsx
+++ b/other/データベース構造.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\take8\OneDrive\ドキュメント\java\material-flow-rate-adjustment\other\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F66453-3B34-483E-B147-60B8264FC579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6F5766-D829-469B-9CF8-A88411CC7F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{099D4C76-A145-49FD-90AD-E407201FC483}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="83">
   <si>
     <t>id
 (INT,
@@ -514,6 +514,38 @@
     <t>new_unit
 (VARCHAR(10),
 UPDATABLE=FALSE)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アカウントと製品履歴だけは重要なデータであるため、完全な履歴を残す。</t>
+    <rPh sb="6" eb="8">
+      <t>セイヒン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>カンゼン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>リレキ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ノコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>それ以外のテーブルについては要検討</t>
+    <rPh sb="2" eb="4">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="14" eb="17">
+      <t>ヨウケントウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -570,12 +602,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -622,7 +660,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -647,9 +685,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -657,6 +692,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -682,13 +729,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>693420</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>510540</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -735,13 +782,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>769620</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>586740</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -788,13 +835,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>746760</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>213360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>609600</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -1137,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E535CC99-BAB4-4269-ACB1-CBFC0A25D5CA}">
-  <dimension ref="A1:O51"/>
+  <dimension ref="B1:O57"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="17.09765625" customWidth="1"/>
@@ -1157,177 +1204,150 @@
     <col min="15" max="15" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="8" t="s">
+    <row r="1" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="2" spans="2:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B2" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B3" t="s">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B3" s="14"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.45">
-      <c r="B4" s="1" t="s">
+    <row r="5" spans="2:11" ht="90" x14ac:dyDescent="0.45">
+      <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="3"/>
+      <c r="E6" s="3">
+        <v>1000</v>
+      </c>
       <c r="F6" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>57</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B8" s="3">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="G9" s="7"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
-        <v>69</v>
-      </c>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
       <c r="G10" s="7"/>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:11" ht="90" x14ac:dyDescent="0.45">
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="I11" s="7"/>
+    </row>
+    <row r="12" spans="2:11" ht="90" x14ac:dyDescent="0.45">
+      <c r="B12" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G12" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I12" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K12" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B12" s="3">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3">
-        <v>1</v>
-      </c>
-      <c r="D12" s="3">
-        <v>2020</v>
-      </c>
-      <c r="E12" s="3">
-        <v>11</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G12" s="10">
-        <v>950</v>
-      </c>
-      <c r="H12" s="3">
-        <v>900</v>
-      </c>
-      <c r="I12" s="10">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
-        <f>(0+G12+I12)-H12</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B13" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="3">
         <v>1</v>
@@ -1336,268 +1356,278 @@
         <v>2020</v>
       </c>
       <c r="E13" s="3">
+        <v>11</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="9">
+        <v>950</v>
+      </c>
+      <c r="H13" s="3">
+        <v>900</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3">
+        <f>(0+G13+I13)-H13</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B14" s="3">
+        <v>2</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>2020</v>
+      </c>
+      <c r="E14" s="3">
         <v>12</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F14" s="3">
         <v>1500</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G14" s="9">
         <v>1550</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="I13" s="10">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3">
-        <f>(J12+G13+I13)-H13</f>
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B14" s="3">
-        <v>3</v>
-      </c>
-      <c r="C14" s="3">
-        <v>1</v>
-      </c>
-      <c r="D14" s="3">
-        <v>2021</v>
-      </c>
-      <c r="E14" s="3">
-        <v>1</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G14" s="10">
-        <v>1000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>1050</v>
-      </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <v>0</v>
       </c>
       <c r="J14" s="3">
         <f>(J13+G14+I14)-H14</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B15" s="3">
+        <v>3</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2021</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="9">
+        <v>1000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1050</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <f>(J14+G15+I15)-H15</f>
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="90" x14ac:dyDescent="0.45">
-      <c r="B18" s="1" t="s">
+    <row r="19" spans="2:11" ht="90" x14ac:dyDescent="0.45">
+      <c r="B19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K19" s="5" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B19" s="3">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4">
-        <v>44136.424305555556</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1111</v>
-      </c>
-      <c r="F19" s="2">
-        <v>50</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B20" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
       </c>
       <c r="D20" s="4">
-        <v>44136.690972222219</v>
+        <v>44136.424305555556</v>
       </c>
       <c r="E20" s="2">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="F20" s="2">
         <v>50</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B21" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" s="3">
         <v>1</v>
       </c>
       <c r="D21" s="4">
-        <v>44137.420138888891</v>
+        <v>44136.690972222219</v>
       </c>
       <c r="E21" s="2">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="F21" s="2">
         <v>50</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B22" s="3">
+        <v>3</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4">
+        <v>44137.420138888891</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1115</v>
+      </c>
+      <c r="F22" s="2">
+        <v>50</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="3"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="90" x14ac:dyDescent="0.45">
-      <c r="B25" s="1" t="s">
+    <row r="26" spans="2:11" ht="90" x14ac:dyDescent="0.45">
+      <c r="B26" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K25" s="5" t="s">
+      <c r="K26" s="5" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B26" s="3">
-        <v>1</v>
-      </c>
-      <c r="C26" s="3">
-        <v>1</v>
-      </c>
-      <c r="D26" s="4">
-        <v>44136.424305555556</v>
-      </c>
-      <c r="E26" s="2">
-        <v>10</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B27" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="3">
         <v>1</v>
       </c>
       <c r="D27" s="4">
-        <v>44136.690972222219</v>
+        <v>44136.424305555556</v>
       </c>
       <c r="E27" s="2">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>21</v>
@@ -1605,507 +1635,554 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B28" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
       </c>
       <c r="D28" s="4">
-        <v>44137.420138888891</v>
+        <v>44136.690972222219</v>
       </c>
       <c r="E28" s="2">
         <v>-5</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
+      <c r="B29" s="3">
+        <v>3</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1</v>
+      </c>
+      <c r="D29" s="4">
+        <v>44137.420138888891</v>
+      </c>
+      <c r="E29" s="2">
+        <v>-5</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" s="3"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="90" x14ac:dyDescent="0.45">
-      <c r="B32" s="1" t="s">
+    <row r="33" spans="2:13" ht="90" x14ac:dyDescent="0.45">
+      <c r="B33" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B33" s="3">
-        <v>1</v>
-      </c>
-      <c r="C33" s="2" t="s">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B34" s="3">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B34" s="3">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B35" s="3">
         <v>2</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B35" s="3">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B36" s="3">
         <v>3</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B36" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="38" spans="1:15" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A38" s="8" t="s">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B39" s="12"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+    </row>
+    <row r="40" spans="2:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="41" spans="2:13" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B41" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B39" t="s">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B42" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B43" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B44" s="11"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="90" x14ac:dyDescent="0.45">
-      <c r="B40" s="1" t="s">
+    <row r="46" spans="2:13" ht="90" x14ac:dyDescent="0.45">
+      <c r="B46" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F46" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J46" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="K46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="M46" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B41" s="3">
-        <v>1</v>
-      </c>
-      <c r="C41" s="2">
-        <v>1</v>
-      </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2" t="s">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B47" s="3">
+        <v>1</v>
+      </c>
+      <c r="C47" s="2">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2" t="s">
+      <c r="F47" s="2"/>
+      <c r="G47" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2" t="s">
+      <c r="H47" s="2"/>
+      <c r="I47" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="J47" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K41" s="2">
-        <v>1</v>
-      </c>
-      <c r="L41" s="2" t="s">
+      <c r="K47" s="2">
+        <v>1</v>
+      </c>
+      <c r="L47" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M41" s="4">
+      <c r="M47" s="4">
         <v>44136.424305555556</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B42" s="3">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.45">
+      <c r="B48" s="3">
         <v>2</v>
       </c>
-      <c r="C42" s="2">
-        <v>1</v>
-      </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2" t="s">
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="I48" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="J48" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="K42" s="2">
-        <v>1</v>
-      </c>
-      <c r="L42" s="2" t="s">
+      <c r="K48" s="2">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="M42" s="4">
+      <c r="M48" s="4">
         <v>44136.690972222219</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B43" s="3">
-        <v>3</v>
-      </c>
-      <c r="C43" s="2">
-        <v>1</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K43" s="2">
-        <v>2</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M43" s="4">
-        <v>44137.420138888891</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B46" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" ht="90" x14ac:dyDescent="0.45">
-      <c r="B47" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B48" s="3">
-        <v>1</v>
-      </c>
-      <c r="C48" s="2">
-        <v>1</v>
-      </c>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M48" s="2">
-        <v>1</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="O48" s="4">
-        <v>44136.424305555556</v>
       </c>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B49" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
       </c>
-      <c r="D49" s="2"/>
+      <c r="D49" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H49" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K49" s="2">
+        <v>2</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M49" s="4">
+        <v>44137.420138888891</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" ht="90" x14ac:dyDescent="0.45">
+      <c r="B53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B54" s="3">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2">
+        <v>1</v>
+      </c>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="L54" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M54" s="2">
+        <v>1</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O54" s="4">
+        <v>44136.424305555556</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B55" s="3">
+        <v>2</v>
+      </c>
+      <c r="C55" s="2">
+        <v>1</v>
+      </c>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K55" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="L55" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M49" s="2">
-        <v>1</v>
-      </c>
-      <c r="N49" s="2" t="s">
+      <c r="M55" s="2">
+        <v>1</v>
+      </c>
+      <c r="N55" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O49" s="4">
+      <c r="O55" s="4">
         <v>44136.690972222219</v>
       </c>
     </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B50" s="3">
+    <row r="56" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B56" s="3">
         <v>3</v>
       </c>
-      <c r="C50" s="2">
-        <v>1</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2" t="s">
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2" t="s">
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2" t="s">
+      <c r="K56" s="2"/>
+      <c r="L56" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M50" s="2">
+      <c r="M56" s="2">
         <v>2</v>
       </c>
-      <c r="N50" s="2" t="s">
+      <c r="N56" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="O50" s="4">
+      <c r="O56" s="4">
         <v>44137.420138888891</v>
       </c>
     </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="N51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="O51" s="3" t="s">
+    <row r="57" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O57" s="3" t="s">
         <v>9</v>
       </c>
     </row>
